--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -131,14 +131,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,7 +420,8 @@
   <cols>
     <col min="1" max="2" width="20.6328125" customWidth="1"/>
     <col min="3" max="3" width="23.26953125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" style="2" customWidth="1"/>
+    <col min="5" max="7" width="12" style="2"/>
     <col min="8" max="8" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -434,38 +435,38 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="H3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="H4" s="4"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="H5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="H5" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,12 +22,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>子产品代码*</t>
-  </si>
-  <si>
-    <t>业绩比较基准生效日（yyyy-mm-dd）*</t>
-  </si>
-  <si>
-    <t>业绩比较基准生效截止日（yyyy-mm-dd）*</t>
   </si>
   <si>
     <t>中债新综合全价指数收益率【系数】%</t>
@@ -59,6 +53,14 @@
       </rPr>
       <t>%</t>
     </r>
+  </si>
+  <si>
+    <t>业绩比较基准生效日（yyyy/mm/dd）*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>业绩比较基准生效截止日（yyyy/mm/dd）*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -416,54 +418,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="20.6328125" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
+    <col min="1" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" customWidth="1"/>
     <col min="5" max="7" width="12" style="2"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="70" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="54" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="H5" s="3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/Performance001.xlsx
@@ -126,7 +126,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -141,6 +141,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,8 +426,9 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.25" style="6" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" customWidth="1"/>
     <col min="5" max="7" width="12" style="2"/>
     <col min="8" max="8" width="15.375" customWidth="1"/>
@@ -431,10 +438,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -451,23 +458,15 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
       <c r="H5" s="3"/>
     </row>
   </sheetData>
